--- a/output/Tables/Best practice/HIA_area_2019_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_area_2019_1000replicate.xlsx
@@ -1,120 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F1297D-9BA4-BD4C-BFA5-7A15FCE4EDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37440" yWindow="-1440" windowWidth="25960" windowHeight="16780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>area_type</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>periurban</t>
-  </si>
-  <si>
-    <t>rural</t>
-  </si>
-  <si>
-    <t>urban</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>Morbidity</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -214,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -248,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -283,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -459,78 +350,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>area_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C2">
-        <v>17297.014999999999</v>
+        <v>14909.166</v>
       </c>
       <c r="D2">
-        <v>15546.688</v>
+        <v>13343.054</v>
       </c>
       <c r="E2">
-        <v>19051.460999999999</v>
+        <v>16475.047</v>
       </c>
       <c r="F2">
-        <v>156123.48499999999</v>
+        <v>141587.534</v>
       </c>
       <c r="G2">
-        <v>145839.976</v>
+        <v>131821.267</v>
       </c>
       <c r="H2">
-        <v>166468.978</v>
+        <v>151343.044</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -542,39 +465,43 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>20765612100.155998</v>
+        <v>18831156916.088</v>
       </c>
       <c r="M2">
-        <v>19391149302.275002</v>
+        <v>17528312202.813</v>
       </c>
       <c r="N2">
-        <v>22139529088.147999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
+        <v>20135217078.669</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C3">
-        <v>14421.137000000001</v>
+        <v>12370.875</v>
       </c>
       <c r="D3">
-        <v>13027.762000000001</v>
+        <v>11087.406</v>
       </c>
       <c r="E3">
-        <v>15809.741</v>
+        <v>13648.571</v>
       </c>
       <c r="F3">
-        <v>150023.90400000001</v>
+        <v>133935.834</v>
       </c>
       <c r="G3">
-        <v>140191.30600000001</v>
+        <v>124507.092</v>
       </c>
       <c r="H3">
-        <v>159888.71599999999</v>
+        <v>143356.456</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -586,39 +513,43 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>19950665546.292999</v>
+        <v>17811526267.08</v>
       </c>
       <c r="M3">
-        <v>18638561066.203999</v>
+        <v>16553728276.343</v>
       </c>
       <c r="N3">
-        <v>21275044775.269001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
+        <v>19077936421.562</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C4">
-        <v>26774.77</v>
+        <v>24079.038</v>
       </c>
       <c r="D4">
-        <v>24775.445</v>
+        <v>22222.263</v>
       </c>
       <c r="E4">
-        <v>28763.489000000001</v>
+        <v>25932.126</v>
       </c>
       <c r="F4">
-        <v>298583.00400000002</v>
+        <v>276756.609</v>
       </c>
       <c r="G4">
-        <v>284898.49599999998</v>
+        <v>263591.87</v>
       </c>
       <c r="H4">
-        <v>312266.26899999997</v>
+        <v>289902.12</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -630,567 +561,619 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>39717138240.379997</v>
+        <v>36815277189.272</v>
       </c>
       <c r="M4">
-        <v>37892182879.654999</v>
+        <v>35058919540.598</v>
       </c>
       <c r="N4">
-        <v>41553182267.877998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
+        <v>38578851567.781</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C5">
-        <v>11472.924999999999</v>
+        <v>9887.094999999999</v>
       </c>
       <c r="D5">
-        <v>10435.808000000001</v>
+        <v>8929.546</v>
       </c>
       <c r="E5">
-        <v>12524.763000000001</v>
+        <v>10860.148</v>
       </c>
       <c r="F5">
-        <v>9321.3549999999996</v>
+        <v>13340.645</v>
       </c>
       <c r="G5">
-        <v>8541.73</v>
+        <v>12144.341</v>
       </c>
       <c r="H5">
-        <v>10112.540000000001</v>
+        <v>14551.127</v>
       </c>
       <c r="I5">
-        <v>639083997.09899998</v>
+        <v>521077101.459</v>
       </c>
       <c r="J5">
-        <v>581084801.82700002</v>
+        <v>470382745.078</v>
       </c>
       <c r="K5">
-        <v>697712548.82200003</v>
+        <v>572365724.801</v>
       </c>
       <c r="L5">
-        <v>1239723582.9790001</v>
+        <v>1774227567.294</v>
       </c>
       <c r="M5">
-        <v>1135789542.2609999</v>
+        <v>1615414715.083</v>
       </c>
       <c r="N5">
-        <v>1345159125.1429999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
+        <v>1935616582.552</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C6">
-        <v>9713.3770000000004</v>
+        <v>8469.897999999999</v>
       </c>
       <c r="D6">
-        <v>8827.1859999999997</v>
+        <v>7613.433</v>
       </c>
       <c r="E6">
-        <v>10613.922</v>
+        <v>9346.842000000001</v>
       </c>
       <c r="F6">
-        <v>8712.0759999999991</v>
+        <v>11588.224</v>
       </c>
       <c r="G6">
-        <v>7948.56</v>
+        <v>10507.536</v>
       </c>
       <c r="H6">
-        <v>9497.7720000000008</v>
+        <v>12697.665</v>
       </c>
       <c r="I6">
-        <v>541206377.41700006</v>
+        <v>446488154.449</v>
       </c>
       <c r="J6">
-        <v>491723496.44300002</v>
+        <v>401222127.786</v>
       </c>
       <c r="K6">
-        <v>591471577.33700001</v>
+        <v>492685974.969</v>
       </c>
       <c r="L6">
-        <v>1159009885.987</v>
+        <v>1541656802.588</v>
       </c>
       <c r="M6">
-        <v>1057506195.558</v>
+        <v>1398309300.246</v>
       </c>
       <c r="N6">
-        <v>1263354825.243</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
+        <v>1688643744.518</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C7">
-        <v>18947.677</v>
+        <v>16901.784</v>
       </c>
       <c r="D7">
-        <v>17723.088</v>
+        <v>15755.053</v>
       </c>
       <c r="E7">
-        <v>20182.937000000002</v>
+        <v>18058.885</v>
       </c>
       <c r="F7">
-        <v>17888.350999999999</v>
+        <v>23713.558</v>
       </c>
       <c r="G7">
-        <v>16861.307000000001</v>
+        <v>22242.818</v>
       </c>
       <c r="H7">
-        <v>18927.608</v>
+        <v>25200.218</v>
       </c>
       <c r="I7">
-        <v>1055517058.74</v>
+        <v>890813111.6390001</v>
       </c>
       <c r="J7">
-        <v>987045327.94000006</v>
+        <v>830041644.249</v>
       </c>
       <c r="K7">
-        <v>1124508490.1340001</v>
+        <v>951945745.265</v>
       </c>
       <c r="L7">
-        <v>2379377282.0760002</v>
+        <v>3154004084.782</v>
       </c>
       <c r="M7">
-        <v>2242452418.4790001</v>
+        <v>2959208330.132</v>
       </c>
       <c r="N7">
-        <v>2517129625.9510002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>3350690872.201</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C8">
-        <v>8092.6909999999998</v>
+        <v>2282.921</v>
       </c>
       <c r="D8">
-        <v>7286.1379999999999</v>
+        <v>2010.192</v>
       </c>
       <c r="E8">
-        <v>8935.8709999999992</v>
+        <v>2569.383</v>
       </c>
       <c r="F8">
-        <v>11163.710999999999</v>
+        <v>1054.172</v>
       </c>
       <c r="G8">
-        <v>9772.1010000000006</v>
+        <v>937.26</v>
       </c>
       <c r="H8">
-        <v>12720.468000000001</v>
+        <v>1177.534</v>
       </c>
       <c r="I8">
-        <v>119799970.005</v>
+        <v>66911652.982</v>
       </c>
       <c r="J8">
-        <v>107881367.13600001</v>
+        <v>58924379.649</v>
       </c>
       <c r="K8">
-        <v>132329000.068</v>
+        <v>75282642.949</v>
       </c>
       <c r="L8">
-        <v>1484571859.938</v>
+        <v>140178556.091</v>
       </c>
       <c r="M8">
-        <v>1299104700.723</v>
+        <v>124590036.352</v>
       </c>
       <c r="N8">
-        <v>1691703090.908</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
+        <v>156513225.751</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C9">
-        <v>6844.6180000000004</v>
+        <v>1910.346</v>
       </c>
       <c r="D9">
-        <v>6181.848</v>
+        <v>1682.584</v>
       </c>
       <c r="E9">
-        <v>7539.55</v>
+        <v>2150.336</v>
       </c>
       <c r="F9">
-        <v>9568.643</v>
+        <v>890.95</v>
       </c>
       <c r="G9">
-        <v>8494.3610000000008</v>
+        <v>791.8869999999999</v>
       </c>
       <c r="H9">
-        <v>10734.445</v>
+        <v>994.84</v>
       </c>
       <c r="I9">
-        <v>101309575.76199999</v>
+        <v>55991452.175</v>
       </c>
       <c r="J9">
-        <v>91513640.325000003</v>
+        <v>49343882.045</v>
       </c>
       <c r="K9">
-        <v>111672984.301</v>
+        <v>63066810.125</v>
       </c>
       <c r="L9">
-        <v>1272156968.585</v>
+        <v>118445086.057</v>
       </c>
       <c r="M9">
-        <v>1130083001.3099999</v>
+        <v>105275014.723</v>
       </c>
       <c r="N9">
-        <v>1427687095.546</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
+        <v>132403821.812</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C10">
-        <v>16267.713</v>
+        <v>4000.595</v>
       </c>
       <c r="D10">
-        <v>15186.183000000001</v>
+        <v>3683.331</v>
       </c>
       <c r="E10">
-        <v>17394.517</v>
+        <v>4328.651</v>
       </c>
       <c r="F10">
-        <v>26280.255000000001</v>
+        <v>1911.875</v>
       </c>
       <c r="G10">
-        <v>24223.909</v>
+        <v>1767.835</v>
       </c>
       <c r="H10">
-        <v>28451.792000000001</v>
+        <v>2059.432</v>
       </c>
       <c r="I10">
-        <v>240891229.83700001</v>
+        <v>117292189.533</v>
       </c>
       <c r="J10">
-        <v>224859849.87799999</v>
+        <v>107990634.671</v>
       </c>
       <c r="K10">
-        <v>257653995.72099999</v>
+        <v>126966837.367</v>
       </c>
       <c r="L10">
-        <v>3494967615.9460001</v>
+        <v>254252076.573</v>
       </c>
       <c r="M10">
-        <v>3222948265.5949998</v>
+        <v>235215630.922</v>
       </c>
       <c r="N10">
-        <v>3783553944.5159998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
+        <v>273766624.803</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C11">
-        <v>1600.047</v>
+        <v>1415.266</v>
       </c>
       <c r="D11">
-        <v>1437.4739999999999</v>
+        <v>1276.19</v>
       </c>
       <c r="E11">
-        <v>1770.453</v>
+        <v>1558.692</v>
       </c>
       <c r="F11">
-        <v>2861.8809999999999</v>
+        <v>2768.983</v>
       </c>
       <c r="G11">
-        <v>2563.2530000000002</v>
+        <v>2472.71</v>
       </c>
       <c r="H11">
-        <v>3174.3960000000002</v>
+        <v>3086.021</v>
       </c>
       <c r="I11">
-        <v>120341117.529</v>
+        <v>55483580.44</v>
       </c>
       <c r="J11">
-        <v>108033332.419</v>
+        <v>50035746.094</v>
       </c>
       <c r="K11">
-        <v>133122961.199</v>
+        <v>61104205.132</v>
       </c>
       <c r="L11">
-        <v>380643427.11500001</v>
+        <v>368330110.739</v>
       </c>
       <c r="M11">
-        <v>340935925.64200002</v>
+        <v>328610246.332</v>
       </c>
       <c r="N11">
-        <v>422261729.86199999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
+        <v>410291410.472</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C12">
-        <v>1440.7819999999999</v>
+        <v>1287.141</v>
       </c>
       <c r="D12">
-        <v>1293.136</v>
+        <v>1153.29</v>
       </c>
       <c r="E12">
-        <v>1594.855</v>
+        <v>1425.059</v>
       </c>
       <c r="F12">
-        <v>2647.5749999999998</v>
+        <v>2386.175</v>
       </c>
       <c r="G12">
-        <v>2369.5059999999999</v>
+        <v>2126.755</v>
       </c>
       <c r="H12">
-        <v>2939.902</v>
+        <v>2659.278</v>
       </c>
       <c r="I12">
-        <v>108370155.88699999</v>
+        <v>50462613.997</v>
       </c>
       <c r="J12">
-        <v>97336795.150999993</v>
+        <v>45232375.72</v>
       </c>
       <c r="K12">
-        <v>119918234.013</v>
+        <v>55873386.677</v>
       </c>
       <c r="L12">
-        <v>352030795.45599997</v>
+        <v>317347494.723</v>
       </c>
       <c r="M12">
-        <v>315312476.41900003</v>
+        <v>282922741.029</v>
       </c>
       <c r="N12">
-        <v>390860248.24400002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
+        <v>353660802.007</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C13">
-        <v>3361.3159999999998</v>
+        <v>3049.87</v>
       </c>
       <c r="D13">
-        <v>3132.5250000000001</v>
+        <v>2847.2</v>
       </c>
       <c r="E13">
-        <v>3596.252</v>
+        <v>3256.739</v>
       </c>
       <c r="F13">
-        <v>6991.6239999999998</v>
+        <v>5195.91</v>
       </c>
       <c r="G13">
-        <v>6501.268</v>
+        <v>4829.343</v>
       </c>
       <c r="H13">
-        <v>7501.7190000000001</v>
+        <v>5578.519</v>
       </c>
       <c r="I13">
-        <v>252797211.37799999</v>
+        <v>119560929.554</v>
       </c>
       <c r="J13">
-        <v>235549603.588</v>
+        <v>111636306.948</v>
       </c>
       <c r="K13">
-        <v>270469842.18900001</v>
+        <v>127665218.925</v>
       </c>
       <c r="L13">
-        <v>929753252.06400001</v>
+        <v>691072853.2589999</v>
       </c>
       <c r="M13">
-        <v>864354678.102</v>
+        <v>641974509.448</v>
       </c>
       <c r="N13">
-        <v>997489931.56500006</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
+        <v>741637932.522</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C14">
-        <v>4169.3649999999998</v>
+        <v>3368.099</v>
       </c>
       <c r="D14">
-        <v>3685.52</v>
+        <v>2951.36</v>
       </c>
       <c r="E14">
-        <v>4658.9430000000002</v>
+        <v>3791.405</v>
       </c>
       <c r="F14">
-        <v>6387.0839999999998</v>
+        <v>3837.057</v>
       </c>
       <c r="G14">
-        <v>5724.1559999999999</v>
+        <v>3353.973</v>
       </c>
       <c r="H14">
-        <v>7064.6490000000003</v>
+        <v>4329.667</v>
       </c>
       <c r="I14">
-        <v>70211776.048999995</v>
+        <v>56072395.902</v>
       </c>
       <c r="J14">
-        <v>62094856.608999997</v>
+        <v>49147027.806</v>
       </c>
       <c r="K14">
-        <v>78461542.689999998</v>
+        <v>63129899.263</v>
       </c>
       <c r="L14">
-        <v>849464958.66299999</v>
+        <v>510126506.69</v>
       </c>
       <c r="M14">
-        <v>760911541.57500005</v>
+        <v>446088948.548</v>
       </c>
       <c r="N14">
-        <v>939517362.21399999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
+        <v>575796580.2410001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C15">
-        <v>3218.3139999999999</v>
+        <v>2690.59</v>
       </c>
       <c r="D15">
-        <v>2811.8359999999998</v>
+        <v>2314.136</v>
       </c>
       <c r="E15">
-        <v>3636.6019999999999</v>
+        <v>3078.862</v>
       </c>
       <c r="F15">
-        <v>5523.85</v>
+        <v>3061.341</v>
       </c>
       <c r="G15">
-        <v>4988.174</v>
+        <v>2622.05</v>
       </c>
       <c r="H15">
-        <v>6070.3209999999999</v>
+        <v>3516.331</v>
       </c>
       <c r="I15">
-        <v>54189470.423</v>
+        <v>44778663.776</v>
       </c>
       <c r="J15">
-        <v>47326661.361000001</v>
+        <v>38495397.999</v>
       </c>
       <c r="K15">
-        <v>61180520.443000004</v>
+        <v>51232637.187</v>
       </c>
       <c r="L15">
-        <v>734545449.57700002</v>
+        <v>407079869.898</v>
       </c>
       <c r="M15">
-        <v>663765127.55299997</v>
+        <v>348779166.293</v>
       </c>
       <c r="N15">
-        <v>807677453.11600006</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
+        <v>467843907.136</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C16">
-        <v>6543.415</v>
+        <v>5617.726</v>
       </c>
       <c r="D16">
-        <v>5954.7120000000004</v>
+        <v>5079.057</v>
       </c>
       <c r="E16">
-        <v>7137.3519999999999</v>
+        <v>6161.976</v>
       </c>
       <c r="F16">
-        <v>11338.718999999999</v>
+        <v>6409.9</v>
       </c>
       <c r="G16">
-        <v>10506.971</v>
+        <v>5784.125</v>
       </c>
       <c r="H16">
-        <v>12184.02</v>
+        <v>7050.965</v>
       </c>
       <c r="I16">
-        <v>110187262.65000001</v>
+        <v>93525479.884</v>
       </c>
       <c r="J16">
-        <v>100273396.118</v>
+        <v>84536275.161</v>
       </c>
       <c r="K16">
-        <v>120260463.698</v>
+        <v>102650776.72</v>
       </c>
       <c r="L16">
-        <v>1508452733.675</v>
+        <v>852523796.215</v>
       </c>
       <c r="M16">
-        <v>1397435966.812</v>
+        <v>769526975.0650001</v>
       </c>
       <c r="N16">
-        <v>1620408894.188</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
+        <v>937612331.947</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C17">
-        <v>30571.895</v>
+        <v>29649.009</v>
       </c>
       <c r="D17">
-        <v>27935.269</v>
+        <v>27078.136</v>
       </c>
       <c r="E17">
-        <v>33304.491000000002</v>
+        <v>32233.18</v>
       </c>
       <c r="F17">
-        <v>9158.3590000000004</v>
+        <v>10224.044</v>
       </c>
       <c r="G17">
-        <v>8027.2020000000002</v>
+        <v>9067.876</v>
       </c>
       <c r="H17">
-        <v>10405.254999999999</v>
+        <v>11401.869</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1202,39 +1185,43 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>1218117987.2260001</v>
+        <v>1360136204.227</v>
       </c>
       <c r="M17">
-        <v>1067625703.747</v>
+        <v>1205586515.353</v>
       </c>
       <c r="N17">
-        <v>1384341413.3859999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
+        <v>1516576110.823</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C18">
-        <v>25994.304</v>
+        <v>25634.894</v>
       </c>
       <c r="D18">
-        <v>23952.951000000001</v>
+        <v>23492.117</v>
       </c>
       <c r="E18">
-        <v>28050.901999999998</v>
+        <v>27770.574</v>
       </c>
       <c r="F18">
-        <v>7831.5879999999997</v>
+        <v>8993.398999999999</v>
       </c>
       <c r="G18">
-        <v>7050.549</v>
+        <v>8071.539</v>
       </c>
       <c r="H18">
-        <v>8639.73</v>
+        <v>9918.379000000001</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1246,39 +1233,43 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>1041886858.591</v>
+        <v>1196379484.471</v>
       </c>
       <c r="M18">
-        <v>937609018.22300005</v>
+        <v>1074247281.206</v>
       </c>
       <c r="N18">
-        <v>1149686715.1129999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
+        <v>1319738964.405</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C19">
-        <v>69380.766000000003</v>
+        <v>70936.277</v>
       </c>
       <c r="D19">
-        <v>65632.546000000002</v>
+        <v>66926.166</v>
       </c>
       <c r="E19">
-        <v>73170.717000000004</v>
+        <v>74962.484</v>
       </c>
       <c r="F19">
-        <v>23998.067999999999</v>
+        <v>28532.293</v>
       </c>
       <c r="G19">
-        <v>22319.579000000002</v>
+        <v>26519.898</v>
       </c>
       <c r="H19">
-        <v>25720.649000000001</v>
+        <v>30556.375</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1290,171 +1281,187 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>3192408477.9050002</v>
+        <v>3794767124.604</v>
       </c>
       <c r="M19">
-        <v>2969204899.5739999</v>
+        <v>3529674588.364</v>
       </c>
       <c r="N19">
-        <v>3421886115.882</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
+        <v>4063345008.023</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C20">
-        <v>31205.022000000001</v>
+        <v>8193.861999999999</v>
       </c>
       <c r="D20">
-        <v>28654.169000000002</v>
+        <v>7376.107</v>
       </c>
       <c r="E20">
-        <v>33869.937999999987</v>
+        <v>9048.369999999999</v>
       </c>
       <c r="F20">
-        <v>47012.608999999997</v>
+        <v>3856.997</v>
       </c>
       <c r="G20">
-        <v>42490.370999999999</v>
+        <v>3496.982</v>
       </c>
       <c r="H20">
-        <v>51906.705000000002</v>
+        <v>4231.806</v>
       </c>
       <c r="I20">
-        <v>462000775.60399997</v>
+        <v>240195294.69</v>
       </c>
       <c r="J20">
-        <v>424254857.33899999</v>
+        <v>216258896.365</v>
       </c>
       <c r="K20">
-        <v>501655980.08999997</v>
+        <v>265316290.441</v>
       </c>
       <c r="L20">
-        <v>6251696444.4689999</v>
+        <v>512875718.721</v>
       </c>
       <c r="M20">
-        <v>5652135967.6280003</v>
+        <v>465080681.997</v>
       </c>
       <c r="N20">
-        <v>6902944130.9699993</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
+        <v>562683672.3659999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C21">
-        <v>40133.978999999999</v>
+        <v>35258.777</v>
       </c>
       <c r="D21">
-        <v>36986.081999999988</v>
+        <v>32298.032</v>
       </c>
       <c r="E21">
-        <v>43321.622000000003</v>
+        <v>38265.875</v>
       </c>
       <c r="F21">
-        <v>35921.781999999992</v>
+        <v>48642.427</v>
       </c>
       <c r="G21">
-        <v>33351.597000000002</v>
+        <v>44894.695</v>
       </c>
       <c r="H21">
-        <v>38537.919999999998</v>
+        <v>52449.01</v>
       </c>
       <c r="I21">
-        <v>2235807433.256</v>
+        <v>1858378367.547</v>
       </c>
       <c r="J21">
-        <v>2059853626.21</v>
+        <v>1701646517.113</v>
       </c>
       <c r="K21">
-        <v>2413692616.2930002</v>
+        <v>2016997445.035</v>
       </c>
       <c r="L21">
-        <v>4778110751.0419998</v>
+        <v>6469888454.664</v>
       </c>
       <c r="M21">
-        <v>4435748156.2980003</v>
+        <v>5972932345.461</v>
       </c>
       <c r="N21">
-        <v>5125643576.3369999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
+        <v>6974951199.271</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C22">
-        <v>13931.093999999999</v>
+        <v>11676.415</v>
       </c>
       <c r="D22">
-        <v>12452.067999999999</v>
+        <v>10344.553</v>
       </c>
       <c r="E22">
-        <v>15432.897000000001</v>
+        <v>13032.243</v>
       </c>
       <c r="F22">
-        <v>23249.652999999998</v>
+        <v>13308.298</v>
       </c>
       <c r="G22">
-        <v>21219.300999999999</v>
+        <v>11760.148</v>
       </c>
       <c r="H22">
-        <v>25318.99</v>
+        <v>14896.963</v>
       </c>
       <c r="I22">
-        <v>234588509.12200001</v>
+        <v>194376539.562</v>
       </c>
       <c r="J22">
-        <v>209694914.088</v>
+        <v>172178700.966</v>
       </c>
       <c r="K22">
-        <v>259902526.831</v>
+        <v>217013313.17</v>
       </c>
       <c r="L22">
-        <v>3092463141.915</v>
+        <v>1769730172.803</v>
       </c>
       <c r="M22">
-        <v>2822112635.9400001</v>
+        <v>1564395089.906</v>
       </c>
       <c r="N22">
-        <v>3367603709.5180001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
+        <v>1981252819.324</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C23">
-        <v>125946.965</v>
+        <v>126220.18</v>
       </c>
       <c r="D23">
-        <v>117520.766</v>
+        <v>117496.419</v>
       </c>
       <c r="E23">
-        <v>134526.10999999999</v>
+        <v>134966.238</v>
       </c>
       <c r="F23">
-        <v>40988.014999999999</v>
+        <v>47749.736</v>
       </c>
       <c r="G23">
-        <v>37397.33</v>
+        <v>43659.313</v>
       </c>
       <c r="H23">
-        <v>44765.634000000013</v>
+        <v>51876.623</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1466,83 +1473,91 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>5452413323.7220001</v>
+        <v>6351282813.302</v>
       </c>
       <c r="M23">
-        <v>4974439621.5439997</v>
+        <v>5809508384.923</v>
       </c>
       <c r="N23">
-        <v>5955914244.3809996</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
+        <v>6899660083.250999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C24">
-        <v>6402.1450000000004</v>
+        <v>5752.277</v>
       </c>
       <c r="D24">
-        <v>5863.1350000000002</v>
+        <v>5276.68</v>
       </c>
       <c r="E24">
-        <v>6961.5599999999986</v>
+        <v>6240.49</v>
       </c>
       <c r="F24">
-        <v>12501.08</v>
+        <v>10351.068</v>
       </c>
       <c r="G24">
-        <v>11434.027</v>
+        <v>9428.808000000001</v>
       </c>
       <c r="H24">
-        <v>13616.017</v>
+        <v>11323.818</v>
       </c>
       <c r="I24">
-        <v>481508484.79400003</v>
+        <v>225507123.991</v>
       </c>
       <c r="J24">
-        <v>440919731.15799999</v>
+        <v>206904428.762</v>
       </c>
       <c r="K24">
-        <v>523511037.40100002</v>
+        <v>244642810.734</v>
       </c>
       <c r="L24">
-        <v>1662427474.635</v>
+        <v>1376750458.721</v>
       </c>
       <c r="M24">
-        <v>1520603080.1630001</v>
+        <v>1253507496.809</v>
       </c>
       <c r="N24">
-        <v>1810611909.671</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>23</v>
+        <v>1505590145.001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C25">
-        <v>58492.922000000013</v>
+        <v>51359.079</v>
       </c>
       <c r="D25">
-        <v>53349.894999999997</v>
+        <v>46652.723</v>
       </c>
       <c r="E25">
-        <v>63624.690999999999</v>
+        <v>56055.744</v>
       </c>
       <c r="F25">
-        <v>604730.39299999992</v>
+        <v>552279.977</v>
       </c>
       <c r="G25">
-        <v>570929.77799999993</v>
+        <v>519920.229</v>
       </c>
       <c r="H25">
-        <v>638623.96299999999</v>
+        <v>584601.62</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1554,233 +1569,253 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>80433415886.828995</v>
+        <v>73457960372.44</v>
       </c>
       <c r="M25">
-        <v>75921893248.134003</v>
+        <v>69140960019.754</v>
       </c>
       <c r="N25">
-        <v>84967756131.294998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>15</v>
+        <v>77792005068.01199</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C26">
-        <v>73203.937999999995</v>
+        <v>61511.556</v>
       </c>
       <c r="D26">
-        <v>66326.896999999997</v>
+        <v>55588.478</v>
       </c>
       <c r="E26">
-        <v>80245.982000000004</v>
+        <v>67487.85500000001</v>
       </c>
       <c r="F26">
-        <v>195015.875</v>
+        <v>172812.435</v>
       </c>
       <c r="G26">
-        <v>180468.41800000001</v>
+        <v>159797.427</v>
       </c>
       <c r="H26">
-        <v>209946.28599999999</v>
+        <v>185889.262</v>
       </c>
       <c r="I26">
-        <v>949436860.68200004</v>
+        <v>699544730.783</v>
       </c>
       <c r="J26">
-        <v>859094357.99100006</v>
+        <v>628489898.627</v>
       </c>
       <c r="K26">
-        <v>1041626052.779</v>
+        <v>771882472.145</v>
       </c>
       <c r="L26">
-        <v>25938133916.077</v>
+        <v>22984155861.129</v>
       </c>
       <c r="M26">
-        <v>23995516716.223</v>
+        <v>21248602664.481</v>
       </c>
       <c r="N26">
-        <v>27922511809.660999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
+        <v>24730010988.508</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C27">
-        <v>61632.532000000007</v>
+        <v>52363.74400000001</v>
       </c>
       <c r="D27">
-        <v>56094.718999999997</v>
+        <v>47342.966</v>
       </c>
       <c r="E27">
-        <v>67245.572</v>
+        <v>57420.24400000001</v>
       </c>
       <c r="F27">
-        <v>184307.636</v>
+        <v>160855.923</v>
       </c>
       <c r="G27">
-        <v>171042.45600000001</v>
+        <v>148626.859</v>
       </c>
       <c r="H27">
-        <v>197770.886</v>
+        <v>173142.949</v>
       </c>
       <c r="I27">
-        <v>805075579.48899996</v>
+        <v>597720884.3970001</v>
       </c>
       <c r="J27">
-        <v>727900593.27999997</v>
+        <v>534293783.55</v>
       </c>
       <c r="K27">
-        <v>884243316.09399998</v>
+        <v>662858808.9580001</v>
       </c>
       <c r="L27">
-        <v>24510295504.488998</v>
+        <v>21392435004.817</v>
       </c>
       <c r="M27">
-        <v>22742836885.266998</v>
+        <v>19763261779.84</v>
       </c>
       <c r="N27">
-        <v>26314311112.530998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" t="s">
-        <v>17</v>
+        <v>23040227661.44</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C28">
-        <v>141275.65700000001</v>
+        <v>124585.29</v>
       </c>
       <c r="D28">
-        <v>132404.49900000001</v>
+        <v>116513.07</v>
       </c>
       <c r="E28">
-        <v>150245.264</v>
+        <v>132700.861</v>
       </c>
       <c r="F28">
-        <v>385080.02100000012</v>
+        <v>342520.145</v>
       </c>
       <c r="G28">
-        <v>365311.53</v>
+        <v>324735.889</v>
       </c>
       <c r="H28">
-        <v>405052.05699999997</v>
+        <v>360347.629</v>
       </c>
       <c r="I28">
-        <v>1659392762.605</v>
+        <v>1221191710.61</v>
       </c>
       <c r="J28">
-        <v>1547728177.5239999</v>
+        <v>1134204861.029</v>
       </c>
       <c r="K28">
-        <v>1772892791.7420001</v>
+        <v>1309228578.277</v>
       </c>
       <c r="L28">
-        <v>51222097602.045998</v>
+        <v>45561897124.705</v>
       </c>
       <c r="M28">
-        <v>48588579108.217003</v>
+        <v>43194519574.52899</v>
       </c>
       <c r="N28">
-        <v>53893650779.980003</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
+        <v>47945904337.277</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C29">
-        <v>276112.12699999998</v>
+        <v>238460.59</v>
       </c>
       <c r="D29">
-        <v>254826.11499999999</v>
+        <v>219444.514</v>
       </c>
       <c r="E29">
-        <v>297736.81800000009</v>
+        <v>257608.96</v>
       </c>
       <c r="F29">
-        <v>764403.53200000001</v>
+        <v>676188.503</v>
       </c>
       <c r="G29">
-        <v>716822.40400000021</v>
+        <v>633160.1749999999</v>
       </c>
       <c r="H29">
-        <v>812769.22899999993</v>
+        <v>719379.8399999999</v>
       </c>
       <c r="I29">
-        <v>3413905202.776</v>
+        <v>2518457325.79</v>
       </c>
       <c r="J29">
-        <v>3134723128.7950001</v>
+        <v>2296988543.206</v>
       </c>
       <c r="K29">
-        <v>3698762160.6149998</v>
+        <v>2743969859.38</v>
       </c>
       <c r="L29">
-        <v>101670527022.612</v>
+        <v>89938487990.65102</v>
       </c>
       <c r="M29">
-        <v>95326932709.707016</v>
+        <v>84206384018.85001</v>
       </c>
       <c r="N29">
-        <v>108130473702.172</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" t="s">
-        <v>23</v>
+        <v>95716142987.22501</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chronic diseases</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C30">
-        <v>217619.20499999999</v>
+        <v>98887.10000000001</v>
       </c>
       <c r="D30">
-        <v>201476.22</v>
+        <v>89874.895</v>
       </c>
       <c r="E30">
-        <v>234112.12700000001</v>
+        <v>108006.123</v>
       </c>
       <c r="F30">
-        <v>159673.139</v>
+        <v>219088.023</v>
       </c>
       <c r="G30">
-        <v>145892.62599999999</v>
+        <v>202159.264</v>
       </c>
       <c r="H30">
-        <v>174145.266</v>
+        <v>236176.432</v>
       </c>
       <c r="I30">
-        <v>3413905202.776</v>
+        <v>2518457325.79</v>
       </c>
       <c r="J30">
-        <v>3134723128.7950001</v>
+        <v>2296988543.206</v>
       </c>
       <c r="K30">
-        <v>3698762160.6149998</v>
+        <v>2743969859.38</v>
       </c>
       <c r="L30">
-        <v>21237111135.783001</v>
+        <v>29137150556.46</v>
       </c>
       <c r="M30">
-        <v>19405039461.573002</v>
+        <v>26883891171.722</v>
       </c>
       <c r="N30">
-        <v>23162717570.876999</v>
+        <v>31422153221.929</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/HIA_area_2019_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_area_2019_1000replicate.xlsx
@@ -1782,22 +1782,22 @@
         </is>
       </c>
       <c r="C30">
-        <v>98887.10000000001</v>
+        <v>60881.33100000001</v>
       </c>
       <c r="D30">
-        <v>89874.895</v>
+        <v>55295.372</v>
       </c>
       <c r="E30">
-        <v>108006.123</v>
+        <v>66586.978</v>
       </c>
       <c r="F30">
-        <v>219088.023</v>
+        <v>76158.78999999999</v>
       </c>
       <c r="G30">
-        <v>202159.264</v>
+        <v>69580.633</v>
       </c>
       <c r="H30">
-        <v>236176.432</v>
+        <v>82901.59699999999</v>
       </c>
       <c r="I30">
         <v>2518457325.79</v>
@@ -1809,13 +1809,13 @@
         <v>2743969859.38</v>
       </c>
       <c r="L30">
-        <v>29137150556.46</v>
+        <v>10129244804.909</v>
       </c>
       <c r="M30">
-        <v>26883891171.722</v>
+        <v>9255915614.173</v>
       </c>
       <c r="N30">
-        <v>31422153221.929</v>
+        <v>11024477835.962</v>
       </c>
     </row>
   </sheetData>
